--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-08-01.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-08-01.xlsx
@@ -30541,7 +30541,7 @@
         <v>1827</v>
       </c>
       <c r="B11">
-        <v>12400</v>
+        <v>12407</v>
       </c>
     </row>
   </sheetData>
